--- a/Result/profitability/6625.xlsx
+++ b/Result/profitability/6625.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM43"/>
+  <dimension ref="A1:AM44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5891,6 +5891,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1387</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E44" t="n">
+        <v>363</v>
+      </c>
+      <c r="F44" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="G44" t="n">
+        <v>276</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>19.93%</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>19</v>
+      </c>
+      <c r="J44" t="n">
+        <v>295</v>
+      </c>
+      <c r="K44" t="n">
+        <v>186</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N44" t="n">
+        <v>18.71125</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.26056338028169</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>6.190000000000001</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.3098098098098099</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.09931506849315075</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>6.370000000000001</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.3217171717171718</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
